--- a/performance_tracking/TEAM_ASSETS.xlsx
+++ b/performance_tracking/TEAM_ASSETS.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -726,56 +726,54 @@
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>챔피언 zip 의 model/sj/ 멤버. 팀 결합의 두 축 중 하나</t>
+          <t>챔피언 zip 의 model/sj/ 멤버(submit_045 계열). 팀 결합의 두 축 중 하나. val2022 없음</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>sj_grid_w060</t>
+          <t>sj3way_nv</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>sj</t>
+          <t>sj 재현</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>cowork/sj/sj_final/</t>
+          <t>cowork/sj/new_val/three_way/src/run_way.py --folds 2022,2024</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>sj 자체</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>1080.4252194208</v>
-      </c>
+          <t>sj 재현 (4way x 900회, strict-forward)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>903</v>
+        <v>826.2</v>
       </c>
       <c r="G8" t="n">
-        <v>253507</v>
+        <v>253035</v>
       </c>
       <c r="H8" t="n">
-        <v>2490.2</v>
+        <v>2210.5</v>
       </c>
       <c r="I8" t="n">
-        <v>247472</v>
+        <v>247303</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>현재 채점 최고 (팀 결합본)</t>
+          <t>★배포본과 **다른 구성**(new_val b계열)이라 826.2 로 약간 낮다. harness3.py 의 BANNED_FOLD=2022 가 막고 있었는데 그 정책은 이미 철회됐다. 이걸로 §31 의 팀층 규약 fit(2022)-&gt;eval(2024) 을 처음 돌릴 수 있었다</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>sj_stdmlp</t>
+          <t>sj_grid_w060</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -793,20 +791,62 @@
           <t>sj 자체</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="n">
+        <v>1080.4252194208</v>
+      </c>
       <c r="F9" t="n">
-        <v>916</v>
+        <v>903</v>
       </c>
       <c r="G9" t="n">
         <v>253507</v>
       </c>
       <c r="H9" t="n">
-        <v>2353.1</v>
+        <v>2490.2</v>
       </c>
       <c r="I9" t="n">
         <v>247472</v>
       </c>
       <c r="J9" t="inlineStr">
+        <is>
+          <t>현재 채점 최고 (팀 결합본)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>sj_stdmlp</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>sj</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>cowork/sj/sj_final/</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>sj 자체</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="n">
+        <v>916</v>
+      </c>
+      <c r="G10" t="n">
+        <v>253507</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2353.1</v>
+      </c>
+      <c r="I10" t="n">
+        <v>247472</v>
+      </c>
+      <c r="J10" t="inlineStr">
         <is>
           <t>미채점. val 기준 최고 — S8 3관문 통과</t>
         </is>
@@ -1207,7 +1247,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1246,10 +1286,15 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>sj3way_nv</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>sj_grid_w060</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>sj_stdmlp</t>
         </is>
@@ -1279,10 +1324,11 @@
       <c r="G2" t="n">
         <v>0.8757</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="n">
         <v>0.9831</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>0.9757</v>
       </c>
     </row>
@@ -1310,10 +1356,11 @@
       <c r="G3" t="n">
         <v>0.9503</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="n">
         <v>0.9089</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>0.9036999999999999</v>
       </c>
     </row>
@@ -1341,10 +1388,11 @@
       <c r="G4" t="n">
         <v>0.9035</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="n">
         <v>0.8548</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>0.8526</v>
       </c>
     </row>
@@ -1372,10 +1420,11 @@
       <c r="G5" t="n">
         <v>0.9572000000000001</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="n">
         <v>0.9038</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>0.9016</v>
       </c>
     </row>
@@ -1403,10 +1452,11 @@
       <c r="G6" t="n">
         <v>0.8329</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="n">
         <v>0.8013</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>0.7953</v>
       </c>
     </row>
@@ -1434,72 +1484,91 @@
       <c r="G7" t="n">
         <v>1</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="n">
         <v>0.8953</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>0.892</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>sj_grid_w060</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>0.9831</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0.9089</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0.8548</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0.9038</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.8013</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0.8953</v>
-      </c>
-      <c r="H8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0.9966</v>
-      </c>
+          <t>sj3way_nv</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>sj_grid_w060</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.9831</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.9089</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.8548</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.9038</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.8013</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.8953</v>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.9966</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
           <t>sj_stdmlp</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="B10" t="n">
         <v>0.9757</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C10" t="n">
         <v>0.9036999999999999</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D10" t="n">
         <v>0.8526</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E10" t="n">
         <v>0.9016</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F10" t="n">
         <v>0.7953</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G10" t="n">
         <v>0.892</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="n">
         <v>0.9966</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1514,7 +1583,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1548,51 +1617,39 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>cw + sj3way</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>0.70 / 0.30</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>채택</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>정방향 736.2 · 역방향 1076.7 — 최고</t>
-        </is>
-      </c>
+          <t>── 월전방분할 (시즌 내부 전이) ──</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>+ hw</t>
+          <t>cw + sj3way</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.70 / 0.30</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>기각</t>
+          <t>채택</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>역방향 1068.1 로 하락. F 부분군에선 hw 가 +152 앞서지만 전이 안 됨</t>
+          <t>정방향 736.2 · 역방향 1076.7 — 최고</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>+ yn</t>
+          <t>+ hw</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1607,14 +1664,14 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>sj3way 와 ρ0.9572 — 정보 중복</t>
+          <t>역방향 1068.1 로 하락. F 부분군에선 hw 가 +152 앞서지만 전이 안 됨</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>+ ye</t>
+          <t>+ yn</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1629,29 +1686,167 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ρ(cw) 0.7952 로 팀 최저인데도 0. 단독 574.7 로 신호 부족</t>
+          <t>sj3way 와 ρ0.9572 — 정보 중복</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>+ ye</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>기각</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>ρ(cw) 0.7952 로 팀 최저인데도 0. 단독 574.7 로 신호 부족</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>+ cw_v17_base</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>기각</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>sj 현행과 ρ0.99 — 사실상 같은 모델</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>── §31 규약 fit(2022)→eval(2024) (시즌 간 전이) ──</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>cw + sj3way + hw(정직)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>0.90/0.05/0.05</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>★최고 930.7</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>월분할과 어긋난다 — 여기서는 hw 가 가중을 받는다</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>cw + hw(정직)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>0.90 / 0.10</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>928.7</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>역방향 2476.5 로 이쪽이 더 안정적</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>cw + sj3way</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>0.95 / 0.05</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>927.2</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>cw 단독</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>921.8</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>기준</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>★ 판단</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>미채택</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>두 계기가 갈린다. fit 폴드 2022 는 구조 단절 이전이고 역방향에서는 sj3way 가 해롭다. 제출 점수가 나오면 그것이 결정자다</t>
         </is>
       </c>
     </row>

--- a/performance_tracking/TEAM_ASSETS.xlsx
+++ b/performance_tracking/TEAM_ASSETS.xlsx
@@ -1583,7 +1583,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1831,22 +1831,86 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>★ 판단</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>미채택</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>두 계기가 갈린다. fit 폴드 2022 는 구조 단절 이전이고 역방향에서는 sj3way 가 해롭다. 제출 점수가 나오면 그것이 결정자다</t>
+          <t>── ★중재 fit(2023)→eval(2024) — 배포 동형 ──</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>cw 단독</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>921.8</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>sj3way·hw·ye 전부 가중 0.00 (퇴화 해)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>── 역 fit(2024)→eval(2022) ──</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>cw 단독</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2479.5</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>cw+hw 는 2476.5 로 더 낮다</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>★ 최종 판단</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>cw + sj3way</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>hw 기각</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>네 계기 중 셋이 hw 를 배제한다. 편입하는 것은 §31(fit2022) 하나뿐이고 그 fit 폴드는 구조 단절 이전이다. 단 중재 계기는 fold2023 의 모든 멤버 BSS 가 음수라 가중이 [1,0,0] 으로 퇴화했다 — 약한 증거로 센다</t>
         </is>
       </c>
     </row>
